--- a/Assets/Game/luban/config/general/develop_level.xlsx
+++ b/Assets/Game/luban/config/general/develop_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="15150" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="310">
   <si>
     <t>##var</t>
   </si>
@@ -47,6 +47,9 @@
     <t>player_item</t>
   </si>
   <si>
+    <t>reward</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -62,303 +65,603 @@
     <t>8001001;100</t>
   </si>
   <si>
+    <t>1001003;100</t>
+  </si>
+  <si>
     <t>8001001;200</t>
   </si>
   <si>
+    <t>1001003;200</t>
+  </si>
+  <si>
     <t>8001001;300</t>
   </si>
   <si>
+    <t>1001003;300</t>
+  </si>
+  <si>
     <t>8001001;400</t>
   </si>
   <si>
+    <t>1001003;400</t>
+  </si>
+  <si>
     <t>8001001;500</t>
   </si>
   <si>
+    <t>1001003;500</t>
+  </si>
+  <si>
     <t>8001001;600</t>
   </si>
   <si>
+    <t>1001003;600</t>
+  </si>
+  <si>
     <t>8001001;700</t>
   </si>
   <si>
+    <t>1001003;700</t>
+  </si>
+  <si>
     <t>8001001;800</t>
   </si>
   <si>
+    <t>1001003;800</t>
+  </si>
+  <si>
     <t>8001001;900</t>
   </si>
   <si>
+    <t>1001003;900</t>
+  </si>
+  <si>
     <t>8001001;1000</t>
   </si>
   <si>
+    <t>1001003;1000</t>
+  </si>
+  <si>
     <t>8001001;1100</t>
   </si>
   <si>
+    <t>1001003;1100</t>
+  </si>
+  <si>
     <t>8001001;1200</t>
   </si>
   <si>
+    <t>1001003;1200</t>
+  </si>
+  <si>
     <t>8001001;1300</t>
   </si>
   <si>
+    <t>1001003;1300</t>
+  </si>
+  <si>
     <t>8001001;1400</t>
   </si>
   <si>
+    <t>1001003;1400</t>
+  </si>
+  <si>
     <t>8001001;1500</t>
   </si>
   <si>
+    <t>1001003;1500</t>
+  </si>
+  <si>
     <t>8001001;1600</t>
   </si>
   <si>
+    <t>1001003;1600</t>
+  </si>
+  <si>
     <t>8001001;1700</t>
   </si>
   <si>
+    <t>1001003;1700</t>
+  </si>
+  <si>
     <t>8001001;1800</t>
   </si>
   <si>
+    <t>1001003;1800</t>
+  </si>
+  <si>
     <t>8001001;1900</t>
   </si>
   <si>
+    <t>1001003;1900</t>
+  </si>
+  <si>
     <t>8001001;2000</t>
   </si>
   <si>
+    <t>1001003;2000</t>
+  </si>
+  <si>
     <t>8001001;2100</t>
   </si>
   <si>
+    <t>1001003;2100</t>
+  </si>
+  <si>
     <t>8001001;2200</t>
   </si>
   <si>
+    <t>1001003;2200</t>
+  </si>
+  <si>
     <t>8001001;2300</t>
   </si>
   <si>
+    <t>1001003;2300</t>
+  </si>
+  <si>
     <t>8001001;2400</t>
   </si>
   <si>
+    <t>1001003;2400</t>
+  </si>
+  <si>
     <t>8001001;2500</t>
   </si>
   <si>
+    <t>1001003;2500</t>
+  </si>
+  <si>
     <t>8001001;2600</t>
   </si>
   <si>
+    <t>1001003;2600</t>
+  </si>
+  <si>
     <t>8001001;2700</t>
   </si>
   <si>
+    <t>1001003;2700</t>
+  </si>
+  <si>
     <t>8001001;2800</t>
   </si>
   <si>
+    <t>1001003;2800</t>
+  </si>
+  <si>
     <t>8001001;2900</t>
   </si>
   <si>
+    <t>1001003;2900</t>
+  </si>
+  <si>
     <t>8001001;3000</t>
   </si>
   <si>
+    <t>1001003;3000</t>
+  </si>
+  <si>
     <t>8001001;3100</t>
   </si>
   <si>
+    <t>1001003;3100</t>
+  </si>
+  <si>
     <t>8001001;3200</t>
   </si>
   <si>
+    <t>1001003;3200</t>
+  </si>
+  <si>
     <t>8001001;3300</t>
   </si>
   <si>
+    <t>1001003;3300</t>
+  </si>
+  <si>
     <t>8001001;3400</t>
   </si>
   <si>
+    <t>1001003;3400</t>
+  </si>
+  <si>
     <t>8001001;3500</t>
   </si>
   <si>
+    <t>1001003;3500</t>
+  </si>
+  <si>
     <t>8001001;3600</t>
   </si>
   <si>
+    <t>1001003;3600</t>
+  </si>
+  <si>
     <t>8001001;3700</t>
   </si>
   <si>
+    <t>1001003;3700</t>
+  </si>
+  <si>
     <t>8001001;3800</t>
   </si>
   <si>
+    <t>1001003;3800</t>
+  </si>
+  <si>
     <t>8001001;3900</t>
   </si>
   <si>
+    <t>1001003;3900</t>
+  </si>
+  <si>
     <t>8001001;4000</t>
   </si>
   <si>
+    <t>1001003;4000</t>
+  </si>
+  <si>
     <t>8001001;4100</t>
   </si>
   <si>
+    <t>1001003;4100</t>
+  </si>
+  <si>
     <t>8001001;4200</t>
   </si>
   <si>
+    <t>1001003;4200</t>
+  </si>
+  <si>
     <t>8001001;4300</t>
   </si>
   <si>
+    <t>1001003;4300</t>
+  </si>
+  <si>
     <t>8001001;4400</t>
   </si>
   <si>
+    <t>1001003;4400</t>
+  </si>
+  <si>
     <t>8001001;4500</t>
   </si>
   <si>
+    <t>1001003;4500</t>
+  </si>
+  <si>
     <t>8001001;4600</t>
   </si>
   <si>
+    <t>1001003;4600</t>
+  </si>
+  <si>
     <t>8001001;4700</t>
   </si>
   <si>
+    <t>1001003;4700</t>
+  </si>
+  <si>
     <t>8001001;4800</t>
   </si>
   <si>
+    <t>1001003;4800</t>
+  </si>
+  <si>
     <t>8001001;4900</t>
   </si>
   <si>
+    <t>1001003;4900</t>
+  </si>
+  <si>
     <t>8001001;5000</t>
   </si>
   <si>
+    <t>1001003;5000</t>
+  </si>
+  <si>
     <t>8001001;5100</t>
   </si>
   <si>
+    <t>1001003;5100</t>
+  </si>
+  <si>
     <t>8001001;5200</t>
   </si>
   <si>
+    <t>1001003;5200</t>
+  </si>
+  <si>
     <t>8001001;5300</t>
   </si>
   <si>
+    <t>1001003;5300</t>
+  </si>
+  <si>
     <t>8001001;5400</t>
   </si>
   <si>
+    <t>1001003;5400</t>
+  </si>
+  <si>
     <t>8001001;5500</t>
   </si>
   <si>
+    <t>1001003;5500</t>
+  </si>
+  <si>
     <t>8001001;5600</t>
   </si>
   <si>
+    <t>1001003;5600</t>
+  </si>
+  <si>
     <t>8001001;5700</t>
   </si>
   <si>
+    <t>1001003;5700</t>
+  </si>
+  <si>
     <t>8001001;5800</t>
   </si>
   <si>
+    <t>1001003;5800</t>
+  </si>
+  <si>
     <t>8001001;5900</t>
   </si>
   <si>
+    <t>1001003;5900</t>
+  </si>
+  <si>
     <t>8001001;6000</t>
   </si>
   <si>
+    <t>1001003;6000</t>
+  </si>
+  <si>
     <t>8001001;6100</t>
   </si>
   <si>
+    <t>1001003;6100</t>
+  </si>
+  <si>
     <t>8001001;6200</t>
   </si>
   <si>
+    <t>1001003;6200</t>
+  </si>
+  <si>
     <t>8001001;6300</t>
   </si>
   <si>
+    <t>1001003;6300</t>
+  </si>
+  <si>
     <t>8001001;6400</t>
   </si>
   <si>
+    <t>1001003;6400</t>
+  </si>
+  <si>
     <t>8001001;6500</t>
   </si>
   <si>
+    <t>1001003;6500</t>
+  </si>
+  <si>
     <t>8001001;6600</t>
   </si>
   <si>
+    <t>1001003;6600</t>
+  </si>
+  <si>
     <t>8001001;6700</t>
   </si>
   <si>
+    <t>1001003;6700</t>
+  </si>
+  <si>
     <t>8001001;6800</t>
   </si>
   <si>
+    <t>1001003;6800</t>
+  </si>
+  <si>
     <t>8001001;6900</t>
   </si>
   <si>
+    <t>1001003;6900</t>
+  </si>
+  <si>
     <t>8001001;7000</t>
   </si>
   <si>
+    <t>1001003;7000</t>
+  </si>
+  <si>
     <t>8001001;7100</t>
   </si>
   <si>
+    <t>1001003;7100</t>
+  </si>
+  <si>
     <t>8001001;7200</t>
   </si>
   <si>
+    <t>1001003;7200</t>
+  </si>
+  <si>
     <t>8001001;7300</t>
   </si>
   <si>
+    <t>1001003;7300</t>
+  </si>
+  <si>
     <t>8001001;7400</t>
   </si>
   <si>
+    <t>1001003;7400</t>
+  </si>
+  <si>
     <t>8001001;7500</t>
   </si>
   <si>
+    <t>1001003;7500</t>
+  </si>
+  <si>
     <t>8001001;7600</t>
   </si>
   <si>
+    <t>1001003;7600</t>
+  </si>
+  <si>
     <t>8001001;7700</t>
   </si>
   <si>
+    <t>1001003;7700</t>
+  </si>
+  <si>
     <t>8001001;7800</t>
   </si>
   <si>
+    <t>1001003;7800</t>
+  </si>
+  <si>
     <t>8001001;7900</t>
   </si>
   <si>
+    <t>1001003;7900</t>
+  </si>
+  <si>
     <t>8001001;8000</t>
   </si>
   <si>
+    <t>1001003;8000</t>
+  </si>
+  <si>
     <t>8001001;8100</t>
   </si>
   <si>
+    <t>1001003;8100</t>
+  </si>
+  <si>
     <t>8001001;8200</t>
   </si>
   <si>
+    <t>1001003;8200</t>
+  </si>
+  <si>
     <t>8001001;8300</t>
   </si>
   <si>
+    <t>1001003;8300</t>
+  </si>
+  <si>
     <t>8001001;8400</t>
   </si>
   <si>
+    <t>1001003;8400</t>
+  </si>
+  <si>
     <t>8001001;8500</t>
   </si>
   <si>
+    <t>1001003;8500</t>
+  </si>
+  <si>
     <t>8001001;8600</t>
   </si>
   <si>
+    <t>1001003;8600</t>
+  </si>
+  <si>
     <t>8001001;8700</t>
   </si>
   <si>
+    <t>1001003;8700</t>
+  </si>
+  <si>
     <t>8001001;8800</t>
   </si>
   <si>
+    <t>1001003;8800</t>
+  </si>
+  <si>
     <t>8001001;8900</t>
   </si>
   <si>
+    <t>1001003;8900</t>
+  </si>
+  <si>
     <t>8001001;9000</t>
   </si>
   <si>
+    <t>1001003;9000</t>
+  </si>
+  <si>
     <t>8001001;9100</t>
   </si>
   <si>
+    <t>1001003;9100</t>
+  </si>
+  <si>
     <t>8001001;9200</t>
   </si>
   <si>
+    <t>1001003;9200</t>
+  </si>
+  <si>
     <t>8001001;9300</t>
   </si>
   <si>
+    <t>1001003;9300</t>
+  </si>
+  <si>
     <t>8001001;9400</t>
   </si>
   <si>
+    <t>1001003;9400</t>
+  </si>
+  <si>
     <t>8001001;9500</t>
   </si>
   <si>
+    <t>1001003;9500</t>
+  </si>
+  <si>
     <t>8001001;9600</t>
   </si>
   <si>
+    <t>1001003;9600</t>
+  </si>
+  <si>
     <t>8001001;9700</t>
   </si>
   <si>
+    <t>1001003;9700</t>
+  </si>
+  <si>
     <t>8001001;9800</t>
   </si>
   <si>
+    <t>1001003;9800</t>
+  </si>
+  <si>
     <t>8001001;9900</t>
   </si>
   <si>
+    <t>1001003;9900</t>
+  </si>
+  <si>
     <t>8001001;10000</t>
   </si>
   <si>
+    <t>1001003;10000</t>
+  </si>
+  <si>
     <t>8001002;100</t>
   </si>
   <si>
@@ -657,306 +960,6 @@
   </si>
   <si>
     <t>8001002;10000</t>
-  </si>
-  <si>
-    <t>1001003;100</t>
-  </si>
-  <si>
-    <t>1001003;200</t>
-  </si>
-  <si>
-    <t>1001003;300</t>
-  </si>
-  <si>
-    <t>1001003;400</t>
-  </si>
-  <si>
-    <t>1001003;500</t>
-  </si>
-  <si>
-    <t>1001003;600</t>
-  </si>
-  <si>
-    <t>1001003;700</t>
-  </si>
-  <si>
-    <t>1001003;800</t>
-  </si>
-  <si>
-    <t>1001003;900</t>
-  </si>
-  <si>
-    <t>1001003;1000</t>
-  </si>
-  <si>
-    <t>1001003;1100</t>
-  </si>
-  <si>
-    <t>1001003;1200</t>
-  </si>
-  <si>
-    <t>1001003;1300</t>
-  </si>
-  <si>
-    <t>1001003;1400</t>
-  </si>
-  <si>
-    <t>1001003;1500</t>
-  </si>
-  <si>
-    <t>1001003;1600</t>
-  </si>
-  <si>
-    <t>1001003;1700</t>
-  </si>
-  <si>
-    <t>1001003;1800</t>
-  </si>
-  <si>
-    <t>1001003;1900</t>
-  </si>
-  <si>
-    <t>1001003;2000</t>
-  </si>
-  <si>
-    <t>1001003;2100</t>
-  </si>
-  <si>
-    <t>1001003;2200</t>
-  </si>
-  <si>
-    <t>1001003;2300</t>
-  </si>
-  <si>
-    <t>1001003;2400</t>
-  </si>
-  <si>
-    <t>1001003;2500</t>
-  </si>
-  <si>
-    <t>1001003;2600</t>
-  </si>
-  <si>
-    <t>1001003;2700</t>
-  </si>
-  <si>
-    <t>1001003;2800</t>
-  </si>
-  <si>
-    <t>1001003;2900</t>
-  </si>
-  <si>
-    <t>1001003;3000</t>
-  </si>
-  <si>
-    <t>1001003;3100</t>
-  </si>
-  <si>
-    <t>1001003;3200</t>
-  </si>
-  <si>
-    <t>1001003;3300</t>
-  </si>
-  <si>
-    <t>1001003;3400</t>
-  </si>
-  <si>
-    <t>1001003;3500</t>
-  </si>
-  <si>
-    <t>1001003;3600</t>
-  </si>
-  <si>
-    <t>1001003;3700</t>
-  </si>
-  <si>
-    <t>1001003;3800</t>
-  </si>
-  <si>
-    <t>1001003;3900</t>
-  </si>
-  <si>
-    <t>1001003;4000</t>
-  </si>
-  <si>
-    <t>1001003;4100</t>
-  </si>
-  <si>
-    <t>1001003;4200</t>
-  </si>
-  <si>
-    <t>1001003;4300</t>
-  </si>
-  <si>
-    <t>1001003;4400</t>
-  </si>
-  <si>
-    <t>1001003;4500</t>
-  </si>
-  <si>
-    <t>1001003;4600</t>
-  </si>
-  <si>
-    <t>1001003;4700</t>
-  </si>
-  <si>
-    <t>1001003;4800</t>
-  </si>
-  <si>
-    <t>1001003;4900</t>
-  </si>
-  <si>
-    <t>1001003;5000</t>
-  </si>
-  <si>
-    <t>1001003;5100</t>
-  </si>
-  <si>
-    <t>1001003;5200</t>
-  </si>
-  <si>
-    <t>1001003;5300</t>
-  </si>
-  <si>
-    <t>1001003;5400</t>
-  </si>
-  <si>
-    <t>1001003;5500</t>
-  </si>
-  <si>
-    <t>1001003;5600</t>
-  </si>
-  <si>
-    <t>1001003;5700</t>
-  </si>
-  <si>
-    <t>1001003;5800</t>
-  </si>
-  <si>
-    <t>1001003;5900</t>
-  </si>
-  <si>
-    <t>1001003;6000</t>
-  </si>
-  <si>
-    <t>1001003;6100</t>
-  </si>
-  <si>
-    <t>1001003;6200</t>
-  </si>
-  <si>
-    <t>1001003;6300</t>
-  </si>
-  <si>
-    <t>1001003;6400</t>
-  </si>
-  <si>
-    <t>1001003;6500</t>
-  </si>
-  <si>
-    <t>1001003;6600</t>
-  </si>
-  <si>
-    <t>1001003;6700</t>
-  </si>
-  <si>
-    <t>1001003;6800</t>
-  </si>
-  <si>
-    <t>1001003;6900</t>
-  </si>
-  <si>
-    <t>1001003;7000</t>
-  </si>
-  <si>
-    <t>1001003;7100</t>
-  </si>
-  <si>
-    <t>1001003;7200</t>
-  </si>
-  <si>
-    <t>1001003;7300</t>
-  </si>
-  <si>
-    <t>1001003;7400</t>
-  </si>
-  <si>
-    <t>1001003;7500</t>
-  </si>
-  <si>
-    <t>1001003;7600</t>
-  </si>
-  <si>
-    <t>1001003;7700</t>
-  </si>
-  <si>
-    <t>1001003;7800</t>
-  </si>
-  <si>
-    <t>1001003;7900</t>
-  </si>
-  <si>
-    <t>1001003;8000</t>
-  </si>
-  <si>
-    <t>1001003;8100</t>
-  </si>
-  <si>
-    <t>1001003;8200</t>
-  </si>
-  <si>
-    <t>1001003;8300</t>
-  </si>
-  <si>
-    <t>1001003;8400</t>
-  </si>
-  <si>
-    <t>1001003;8500</t>
-  </si>
-  <si>
-    <t>1001003;8600</t>
-  </si>
-  <si>
-    <t>1001003;8700</t>
-  </si>
-  <si>
-    <t>1001003;8800</t>
-  </si>
-  <si>
-    <t>1001003;8900</t>
-  </si>
-  <si>
-    <t>1001003;9000</t>
-  </si>
-  <si>
-    <t>1001003;9100</t>
-  </si>
-  <si>
-    <t>1001003;9200</t>
-  </si>
-  <si>
-    <t>1001003;9300</t>
-  </si>
-  <si>
-    <t>1001003;9400</t>
-  </si>
-  <si>
-    <t>1001003;9500</t>
-  </si>
-  <si>
-    <t>1001003;9600</t>
-  </si>
-  <si>
-    <t>1001003;9700</t>
-  </si>
-  <si>
-    <t>1001003;9800</t>
-  </si>
-  <si>
-    <t>1001003;9900</t>
-  </si>
-  <si>
-    <t>1001003;10000</t>
   </si>
 </sst>
 </file>
@@ -2144,18 +2147,19 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F305"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="29.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="26" style="2" customWidth="1"/>
     <col min="5" max="5" width="40.75" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="15.625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2171,33 +2175,39 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:5">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:5">
+    <row r="4" s="2" customFormat="1" spans="1:6">
       <c r="B4" s="2">
         <v>1010000</v>
       </c>
@@ -2210,10 +2220,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="B5" s="2">
         <v>1010001</v>
       </c>
@@ -2226,10 +2239,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="B6" s="2">
         <v>1010002</v>
       </c>
@@ -2242,10 +2258,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>14</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="B7" s="2">
         <v>1010003</v>
       </c>
@@ -2258,10 +2277,13 @@
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="B8" s="2">
         <v>1010004</v>
       </c>
@@ -2274,10 +2296,13 @@
         <v>4</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>18</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="B9" s="2">
         <v>1010005</v>
       </c>
@@ -2290,10 +2315,13 @@
         <v>5</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="B10" s="2">
         <v>1010006</v>
       </c>
@@ -2306,10 +2334,13 @@
         <v>6</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>22</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="B11" s="2">
         <v>1010007</v>
       </c>
@@ -2322,10 +2353,13 @@
         <v>7</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>24</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="B12" s="2">
         <v>1010008</v>
       </c>
@@ -2338,10 +2372,13 @@
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>26</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="B13" s="2">
         <v>1010009</v>
       </c>
@@ -2354,10 +2391,13 @@
         <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>28</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="B14" s="2">
         <v>1010010</v>
       </c>
@@ -2370,10 +2410,13 @@
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>30</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="B15" s="2">
         <v>1010011</v>
       </c>
@@ -2386,10 +2429,13 @@
         <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>32</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="B16" s="2">
         <v>1010012</v>
       </c>
@@ -2402,10 +2448,13 @@
         <v>12</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5">
+        <v>34</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
       <c r="B17" s="2">
         <v>1010013</v>
       </c>
@@ -2418,10 +2467,13 @@
         <v>13</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
+        <v>36</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="2">
         <v>1010014</v>
       </c>
@@ -2434,10 +2486,13 @@
         <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
+        <v>38</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
       <c r="B19" s="2">
         <v>1010015</v>
       </c>
@@ -2450,10 +2505,13 @@
         <v>15</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
+        <v>40</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="2">
         <v>1010016</v>
       </c>
@@ -2466,10 +2524,13 @@
         <v>16</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
+        <v>42</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
       <c r="B21" s="2">
         <v>1010017</v>
       </c>
@@ -2482,10 +2543,13 @@
         <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
+        <v>44</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
       <c r="B22" s="2">
         <v>1010018</v>
       </c>
@@ -2498,10 +2562,13 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
+        <v>46</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
       <c r="B23" s="2">
         <v>1010019</v>
       </c>
@@ -2514,10 +2581,13 @@
         <v>19</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
+        <v>48</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
       <c r="B24" s="2">
         <v>1010020</v>
       </c>
@@ -2530,10 +2600,13 @@
         <v>20</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
+        <v>50</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
       <c r="B25" s="2">
         <v>1010021</v>
       </c>
@@ -2546,10 +2619,13 @@
         <v>21</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
+        <v>52</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
       <c r="B26" s="2">
         <v>1010022</v>
       </c>
@@ -2562,10 +2638,13 @@
         <v>22</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
+        <v>54</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="B27" s="2">
         <v>1010023</v>
       </c>
@@ -2578,10 +2657,13 @@
         <v>23</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
+        <v>56</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
       <c r="B28" s="2">
         <v>1010024</v>
       </c>
@@ -2594,10 +2676,13 @@
         <v>24</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
+        <v>58</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
       <c r="B29" s="2">
         <v>1010025</v>
       </c>
@@ -2610,10 +2695,13 @@
         <v>25</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
+        <v>60</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="2">
         <v>1010026</v>
       </c>
@@ -2626,10 +2714,13 @@
         <v>26</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5">
+        <v>62</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
       <c r="B31" s="2">
         <v>1010027</v>
       </c>
@@ -2642,10 +2733,13 @@
         <v>27</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5">
+        <v>64</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="2">
         <v>1010028</v>
       </c>
@@ -2658,10 +2752,13 @@
         <v>28</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
+        <v>66</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
       <c r="B33" s="2">
         <v>1010029</v>
       </c>
@@ -2674,10 +2771,13 @@
         <v>29</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5">
+        <v>68</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="2">
         <v>1010030</v>
       </c>
@@ -2690,10 +2790,13 @@
         <v>30</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5">
+        <v>70</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
       <c r="B35" s="2">
         <v>1010031</v>
       </c>
@@ -2706,10 +2809,13 @@
         <v>31</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5">
+        <v>72</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6">
       <c r="B36" s="2">
         <v>1010032</v>
       </c>
@@ -2722,10 +2828,13 @@
         <v>32</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5">
+        <v>74</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="2">
         <v>1010033</v>
       </c>
@@ -2738,10 +2847,13 @@
         <v>33</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5">
+        <v>76</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6">
       <c r="B38" s="2">
         <v>1010034</v>
       </c>
@@ -2754,10 +2866,13 @@
         <v>34</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5">
+        <v>78</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6">
       <c r="B39" s="2">
         <v>1010035</v>
       </c>
@@ -2770,10 +2885,13 @@
         <v>35</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5">
+        <v>80</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6">
       <c r="B40" s="2">
         <v>1010036</v>
       </c>
@@ -2786,10 +2904,13 @@
         <v>36</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5">
+        <v>82</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="2">
         <v>1010037</v>
       </c>
@@ -2802,10 +2923,13 @@
         <v>37</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5">
+        <v>84</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6">
       <c r="B42" s="2">
         <v>1010038</v>
       </c>
@@ -2818,10 +2942,13 @@
         <v>38</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5">
+        <v>86</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
       <c r="B43" s="2">
         <v>1010039</v>
       </c>
@@ -2834,10 +2961,13 @@
         <v>39</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5">
+        <v>88</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="2">
         <v>1010040</v>
       </c>
@@ -2850,10 +2980,13 @@
         <v>40</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5">
+        <v>90</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
       <c r="B45" s="2">
         <v>1010041</v>
       </c>
@@ -2866,10 +2999,13 @@
         <v>41</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5">
+        <v>92</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
       <c r="B46" s="2">
         <v>1010042</v>
       </c>
@@ -2882,10 +3018,13 @@
         <v>42</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5">
+        <v>94</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6">
       <c r="B47" s="2">
         <v>1010043</v>
       </c>
@@ -2898,10 +3037,13 @@
         <v>43</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5">
+        <v>96</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6">
       <c r="B48" s="2">
         <v>1010044</v>
       </c>
@@ -2914,10 +3056,13 @@
         <v>44</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5">
+        <v>98</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
       <c r="B49" s="2">
         <v>1010045</v>
       </c>
@@ -2930,10 +3075,13 @@
         <v>45</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5">
+        <v>100</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
       <c r="B50" s="2">
         <v>1010046</v>
       </c>
@@ -2946,10 +3094,13 @@
         <v>46</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5">
+        <v>102</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="2">
         <v>1010047</v>
       </c>
@@ -2962,10 +3113,13 @@
         <v>47</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5">
+        <v>104</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="2">
         <v>1010048</v>
       </c>
@@ -2978,10 +3132,13 @@
         <v>48</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5">
+        <v>106</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
       <c r="B53" s="2">
         <v>1010049</v>
       </c>
@@ -2994,10 +3151,13 @@
         <v>49</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5">
+        <v>108</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6">
       <c r="B54" s="2">
         <v>1010050</v>
       </c>
@@ -3010,10 +3170,13 @@
         <v>50</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5">
+        <v>110</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="2">
         <v>1010051</v>
       </c>
@@ -3026,10 +3189,13 @@
         <v>51</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5">
+        <v>112</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
       <c r="B56" s="2">
         <v>1010052</v>
       </c>
@@ -3042,10 +3208,13 @@
         <v>52</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5">
+        <v>114</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6">
       <c r="B57" s="2">
         <v>1010053</v>
       </c>
@@ -3058,10 +3227,13 @@
         <v>53</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5">
+        <v>116</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
       <c r="B58" s="2">
         <v>1010054</v>
       </c>
@@ -3074,10 +3246,13 @@
         <v>54</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5">
+        <v>118</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="2">
         <v>1010055</v>
       </c>
@@ -3090,10 +3265,13 @@
         <v>55</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5">
+        <v>120</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="2">
         <v>1010056</v>
       </c>
@@ -3106,10 +3284,13 @@
         <v>56</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5">
+        <v>122</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
       <c r="B61" s="2">
         <v>1010057</v>
       </c>
@@ -3122,10 +3303,13 @@
         <v>57</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5">
+        <v>124</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
       <c r="B62" s="2">
         <v>1010058</v>
       </c>
@@ -3138,10 +3322,13 @@
         <v>58</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5">
+        <v>126</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6">
       <c r="B63" s="2">
         <v>1010059</v>
       </c>
@@ -3154,10 +3341,13 @@
         <v>59</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5">
+        <v>128</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
       <c r="B64" s="2">
         <v>1010060</v>
       </c>
@@ -3170,10 +3360,13 @@
         <v>60</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5">
+        <v>130</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65" s="2">
         <v>1010061</v>
       </c>
@@ -3186,10 +3379,13 @@
         <v>61</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5">
+        <v>132</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
       <c r="B66" s="2">
         <v>1010062</v>
       </c>
@@ -3202,10 +3398,13 @@
         <v>62</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5">
+        <v>134</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6">
       <c r="B67" s="2">
         <v>1010063</v>
       </c>
@@ -3218,10 +3417,13 @@
         <v>63</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5">
+        <v>136</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6">
       <c r="B68" s="2">
         <v>1010064</v>
       </c>
@@ -3234,10 +3436,13 @@
         <v>64</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5">
+        <v>138</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6">
       <c r="B69" s="2">
         <v>1010065</v>
       </c>
@@ -3250,10 +3455,13 @@
         <v>65</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5">
+        <v>140</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6">
       <c r="B70" s="2">
         <v>1010066</v>
       </c>
@@ -3266,10 +3474,13 @@
         <v>66</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5">
+        <v>142</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
       <c r="B71" s="2">
         <v>1010067</v>
       </c>
@@ -3282,10 +3493,13 @@
         <v>67</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5">
+        <v>144</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6">
       <c r="B72" s="2">
         <v>1010068</v>
       </c>
@@ -3298,10 +3512,13 @@
         <v>68</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5">
+        <v>146</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6">
       <c r="B73" s="2">
         <v>1010069</v>
       </c>
@@ -3314,10 +3531,13 @@
         <v>69</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5">
+        <v>148</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6">
       <c r="B74" s="2">
         <v>1010070</v>
       </c>
@@ -3330,10 +3550,13 @@
         <v>70</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5">
+        <v>150</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6">
       <c r="B75" s="2">
         <v>1010071</v>
       </c>
@@ -3346,10 +3569,13 @@
         <v>71</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5">
+        <v>152</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
       <c r="B76" s="2">
         <v>1010072</v>
       </c>
@@ -3362,10 +3588,13 @@
         <v>72</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5">
+        <v>154</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6">
       <c r="B77" s="2">
         <v>1010073</v>
       </c>
@@ -3378,10 +3607,13 @@
         <v>73</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5">
+        <v>156</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6">
       <c r="B78" s="2">
         <v>1010074</v>
       </c>
@@ -3394,10 +3626,13 @@
         <v>74</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="79" spans="2:5">
+        <v>158</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6">
       <c r="B79" s="2">
         <v>1010075</v>
       </c>
@@ -3410,10 +3645,13 @@
         <v>75</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="80" spans="2:5">
+        <v>160</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
       <c r="B80" s="2">
         <v>1010076</v>
       </c>
@@ -3426,10 +3664,13 @@
         <v>76</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5">
+        <v>162</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6">
       <c r="B81" s="2">
         <v>1010077</v>
       </c>
@@ -3442,10 +3683,13 @@
         <v>77</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5">
+        <v>164</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6">
       <c r="B82" s="2">
         <v>1010078</v>
       </c>
@@ -3458,10 +3702,13 @@
         <v>78</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5">
+        <v>166</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6">
       <c r="B83" s="2">
         <v>1010079</v>
       </c>
@@ -3474,10 +3721,13 @@
         <v>79</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5">
+        <v>168</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6">
       <c r="B84" s="2">
         <v>1010080</v>
       </c>
@@ -3490,10 +3740,13 @@
         <v>80</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5">
+        <v>170</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6">
       <c r="B85" s="2">
         <v>1010081</v>
       </c>
@@ -3506,10 +3759,13 @@
         <v>81</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5">
+        <v>172</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6">
       <c r="B86" s="2">
         <v>1010082</v>
       </c>
@@ -3522,10 +3778,13 @@
         <v>82</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5">
+        <v>174</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6">
       <c r="B87" s="2">
         <v>1010083</v>
       </c>
@@ -3538,10 +3797,13 @@
         <v>83</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5">
+        <v>176</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6">
       <c r="B88" s="2">
         <v>1010084</v>
       </c>
@@ -3554,10 +3816,13 @@
         <v>84</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="89" spans="2:5">
+        <v>178</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6">
       <c r="B89" s="2">
         <v>1010085</v>
       </c>
@@ -3570,10 +3835,13 @@
         <v>85</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5">
+        <v>180</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6">
       <c r="B90" s="2">
         <v>1010086</v>
       </c>
@@ -3586,10 +3854,13 @@
         <v>86</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="91" spans="2:5">
+        <v>182</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6">
       <c r="B91" s="2">
         <v>1010087</v>
       </c>
@@ -3602,10 +3873,13 @@
         <v>87</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="92" spans="2:5">
+        <v>184</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6">
       <c r="B92" s="2">
         <v>1010088</v>
       </c>
@@ -3618,10 +3892,13 @@
         <v>88</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5">
+        <v>186</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6">
       <c r="B93" s="2">
         <v>1010089</v>
       </c>
@@ -3634,10 +3911,13 @@
         <v>89</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5">
+        <v>188</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6">
       <c r="B94" s="2">
         <v>1010090</v>
       </c>
@@ -3650,10 +3930,13 @@
         <v>90</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5">
+        <v>190</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6">
       <c r="B95" s="2">
         <v>1010091</v>
       </c>
@@ -3666,10 +3949,13 @@
         <v>91</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5">
+        <v>192</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6">
       <c r="B96" s="2">
         <v>1010092</v>
       </c>
@@ -3682,10 +3968,13 @@
         <v>92</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5">
+        <v>194</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6">
       <c r="B97" s="2">
         <v>1010093</v>
       </c>
@@ -3698,10 +3987,13 @@
         <v>93</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5">
+        <v>196</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="2">
         <v>1010094</v>
       </c>
@@ -3714,10 +4006,13 @@
         <v>94</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="99" spans="2:5">
+        <v>198</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6">
       <c r="B99" s="2">
         <v>1010095</v>
       </c>
@@ -3730,10 +4025,13 @@
         <v>95</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="100" spans="2:5">
+        <v>200</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
       <c r="B100" s="2">
         <v>1010096</v>
       </c>
@@ -3746,10 +4044,13 @@
         <v>96</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="101" spans="2:5">
+        <v>202</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
       <c r="B101" s="2">
         <v>1010097</v>
       </c>
@@ -3762,10 +4063,13 @@
         <v>97</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="102" spans="2:5">
+        <v>204</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="2">
         <v>1010098</v>
       </c>
@@ -3778,10 +4082,13 @@
         <v>98</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="103" spans="2:5">
+        <v>206</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
       <c r="B103" s="2">
         <v>1010099</v>
       </c>
@@ -3794,10 +4101,13 @@
         <v>99</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="105" spans="2:5">
+        <v>208</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
       <c r="B105" s="2">
         <v>2010000</v>
       </c>
@@ -3810,10 +4120,13 @@
         <v>0</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="106" spans="2:5">
+        <v>210</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6">
       <c r="B106" s="2">
         <v>2010001</v>
       </c>
@@ -3826,10 +4139,13 @@
         <v>1</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="107" spans="2:5">
+        <v>211</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
       <c r="B107" s="2">
         <v>2010002</v>
       </c>
@@ -3842,10 +4158,13 @@
         <v>2</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="108" spans="2:5">
+        <v>212</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="2">
         <v>2010003</v>
       </c>
@@ -3858,10 +4177,13 @@
         <v>3</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="109" spans="2:5">
+        <v>213</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
       <c r="B109" s="2">
         <v>2010004</v>
       </c>
@@ -3874,10 +4196,13 @@
         <v>4</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="110" spans="2:5">
+        <v>214</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
       <c r="B110" s="2">
         <v>2010005</v>
       </c>
@@ -3890,10 +4215,13 @@
         <v>5</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="111" spans="2:5">
+        <v>215</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="111" spans="2:6">
       <c r="B111" s="2">
         <v>2010006</v>
       </c>
@@ -3906,10 +4234,13 @@
         <v>6</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="112" spans="2:5">
+        <v>216</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
       <c r="B112" s="2">
         <v>2010007</v>
       </c>
@@ -3922,10 +4253,13 @@
         <v>7</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="113" spans="2:5">
+        <v>217</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" spans="2:6">
       <c r="B113" s="2">
         <v>2010008</v>
       </c>
@@ -3938,10 +4272,13 @@
         <v>8</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="114" spans="2:5">
+        <v>218</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="114" spans="2:6">
       <c r="B114" s="2">
         <v>2010009</v>
       </c>
@@ -3954,10 +4291,13 @@
         <v>9</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="115" spans="2:5">
+        <v>219</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6">
       <c r="B115" s="2">
         <v>2010010</v>
       </c>
@@ -3970,10 +4310,13 @@
         <v>10</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="116" spans="2:5">
+        <v>220</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6">
       <c r="B116" s="2">
         <v>2010011</v>
       </c>
@@ -3986,10 +4329,13 @@
         <v>11</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="117" spans="2:5">
+        <v>221</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="117" spans="2:6">
       <c r="B117" s="2">
         <v>2010012</v>
       </c>
@@ -4002,10 +4348,13 @@
         <v>12</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="118" spans="2:5">
+        <v>222</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6">
       <c r="B118" s="2">
         <v>2010013</v>
       </c>
@@ -4018,10 +4367,13 @@
         <v>13</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="119" spans="2:5">
+        <v>223</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6">
       <c r="B119" s="2">
         <v>2010014</v>
       </c>
@@ -4034,10 +4386,13 @@
         <v>14</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="120" spans="2:5">
+        <v>224</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6">
       <c r="B120" s="2">
         <v>2010015</v>
       </c>
@@ -4050,10 +4405,13 @@
         <v>15</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="121" spans="2:5">
+        <v>225</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6">
       <c r="B121" s="2">
         <v>2010016</v>
       </c>
@@ -4066,10 +4424,13 @@
         <v>16</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="122" spans="2:5">
+        <v>226</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6">
       <c r="B122" s="2">
         <v>2010017</v>
       </c>
@@ -4082,10 +4443,13 @@
         <v>17</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="123" spans="2:5">
+        <v>227</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="123" spans="2:6">
       <c r="B123" s="2">
         <v>2010018</v>
       </c>
@@ -4098,10 +4462,13 @@
         <v>18</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="124" spans="2:5">
+        <v>228</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6">
       <c r="B124" s="2">
         <v>2010019</v>
       </c>
@@ -4114,10 +4481,13 @@
         <v>19</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="125" spans="2:5">
+        <v>229</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6">
       <c r="B125" s="2">
         <v>2010020</v>
       </c>
@@ -4130,10 +4500,13 @@
         <v>20</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="126" spans="2:5">
+        <v>230</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="126" spans="2:6">
       <c r="B126" s="2">
         <v>2010021</v>
       </c>
@@ -4146,10 +4519,13 @@
         <v>21</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="127" spans="2:5">
+        <v>231</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6">
       <c r="B127" s="2">
         <v>2010022</v>
       </c>
@@ -4162,10 +4538,13 @@
         <v>22</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="128" spans="2:5">
+        <v>232</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="128" spans="2:6">
       <c r="B128" s="2">
         <v>2010023</v>
       </c>
@@ -4178,10 +4557,13 @@
         <v>23</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="129" spans="2:5">
+        <v>233</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="129" spans="2:6">
       <c r="B129" s="2">
         <v>2010024</v>
       </c>
@@ -4194,10 +4576,13 @@
         <v>24</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="130" spans="2:5">
+        <v>234</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="130" spans="2:6">
       <c r="B130" s="2">
         <v>2010025</v>
       </c>
@@ -4210,10 +4595,13 @@
         <v>25</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="131" spans="2:5">
+        <v>235</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6">
       <c r="B131" s="2">
         <v>2010026</v>
       </c>
@@ -4226,10 +4614,13 @@
         <v>26</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="132" spans="2:5">
+        <v>236</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="132" spans="2:6">
       <c r="B132" s="2">
         <v>2010027</v>
       </c>
@@ -4242,10 +4633,13 @@
         <v>27</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="133" spans="2:5">
+        <v>237</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="133" spans="2:6">
       <c r="B133" s="2">
         <v>2010028</v>
       </c>
@@ -4258,10 +4652,13 @@
         <v>28</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="134" spans="2:5">
+        <v>238</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="134" spans="2:6">
       <c r="B134" s="2">
         <v>2010029</v>
       </c>
@@ -4274,10 +4671,13 @@
         <v>29</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="135" spans="2:5">
+        <v>239</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6">
       <c r="B135" s="2">
         <v>2010030</v>
       </c>
@@ -4290,10 +4690,13 @@
         <v>30</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="136" spans="2:5">
+        <v>240</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
       <c r="B136" s="2">
         <v>2010031</v>
       </c>
@@ -4306,10 +4709,13 @@
         <v>31</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="137" spans="2:5">
+        <v>241</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="137" spans="2:6">
       <c r="B137" s="2">
         <v>2010032</v>
       </c>
@@ -4322,10 +4728,13 @@
         <v>32</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="138" spans="2:5">
+        <v>242</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="138" spans="2:6">
       <c r="B138" s="2">
         <v>2010033</v>
       </c>
@@ -4338,10 +4747,13 @@
         <v>33</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="139" spans="2:5">
+        <v>243</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="139" spans="2:6">
       <c r="B139" s="2">
         <v>2010034</v>
       </c>
@@ -4354,10 +4766,13 @@
         <v>34</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="140" spans="2:5">
+        <v>244</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
       <c r="B140" s="2">
         <v>2010035</v>
       </c>
@@ -4370,10 +4785,13 @@
         <v>35</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="141" spans="2:5">
+        <v>245</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
       <c r="B141" s="2">
         <v>2010036</v>
       </c>
@@ -4386,10 +4804,13 @@
         <v>36</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="142" spans="2:5">
+        <v>246</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="142" spans="2:6">
       <c r="B142" s="2">
         <v>2010037</v>
       </c>
@@ -4402,10 +4823,13 @@
         <v>37</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="143" spans="2:5">
+        <v>247</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="143" spans="2:6">
       <c r="B143" s="2">
         <v>2010038</v>
       </c>
@@ -4418,10 +4842,13 @@
         <v>38</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="144" spans="2:5">
+        <v>248</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6">
       <c r="B144" s="2">
         <v>2010039</v>
       </c>
@@ -4434,10 +4861,13 @@
         <v>39</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="145" spans="2:5">
+        <v>249</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="145" spans="2:6">
       <c r="B145" s="2">
         <v>2010040</v>
       </c>
@@ -4450,10 +4880,13 @@
         <v>40</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="146" spans="2:5">
+        <v>250</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6">
       <c r="B146" s="2">
         <v>2010041</v>
       </c>
@@ -4466,10 +4899,13 @@
         <v>41</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="147" spans="2:5">
+        <v>251</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6">
       <c r="B147" s="2">
         <v>2010042</v>
       </c>
@@ -4482,10 +4918,13 @@
         <v>42</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="148" spans="2:5">
+        <v>252</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="148" spans="2:6">
       <c r="B148" s="2">
         <v>2010043</v>
       </c>
@@ -4498,10 +4937,13 @@
         <v>43</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="149" spans="2:5">
+        <v>253</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6">
       <c r="B149" s="2">
         <v>2010044</v>
       </c>
@@ -4514,10 +4956,13 @@
         <v>44</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="150" spans="2:5">
+        <v>254</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6">
       <c r="B150" s="2">
         <v>2010045</v>
       </c>
@@ -4530,10 +4975,13 @@
         <v>45</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="151" spans="2:5">
+        <v>255</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6">
       <c r="B151" s="2">
         <v>2010046</v>
       </c>
@@ -4546,10 +4994,13 @@
         <v>46</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="152" spans="2:5">
+        <v>256</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6">
       <c r="B152" s="2">
         <v>2010047</v>
       </c>
@@ -4562,10 +5013,13 @@
         <v>47</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="153" spans="2:5">
+        <v>257</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6">
       <c r="B153" s="2">
         <v>2010048</v>
       </c>
@@ -4578,10 +5032,13 @@
         <v>48</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="154" spans="2:5">
+        <v>258</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="154" spans="2:6">
       <c r="B154" s="2">
         <v>2010049</v>
       </c>
@@ -4594,10 +5051,13 @@
         <v>49</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="155" spans="2:5">
+        <v>259</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="155" spans="2:6">
       <c r="B155" s="2">
         <v>2010050</v>
       </c>
@@ -4610,10 +5070,13 @@
         <v>50</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="156" spans="2:5">
+        <v>260</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6">
       <c r="B156" s="2">
         <v>2010051</v>
       </c>
@@ -4626,10 +5089,13 @@
         <v>51</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="157" spans="2:5">
+        <v>261</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6">
       <c r="B157" s="2">
         <v>2010052</v>
       </c>
@@ -4642,10 +5108,13 @@
         <v>52</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="158" spans="2:5">
+        <v>262</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="158" spans="2:6">
       <c r="B158" s="2">
         <v>2010053</v>
       </c>
@@ -4658,10 +5127,13 @@
         <v>53</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="159" spans="2:5">
+        <v>263</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="159" spans="2:6">
       <c r="B159" s="2">
         <v>2010054</v>
       </c>
@@ -4674,10 +5146,13 @@
         <v>54</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="160" spans="2:5">
+        <v>264</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6">
       <c r="B160" s="2">
         <v>2010055</v>
       </c>
@@ -4690,10 +5165,13 @@
         <v>55</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="161" spans="2:5">
+        <v>265</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="161" spans="2:6">
       <c r="B161" s="2">
         <v>2010056</v>
       </c>
@@ -4706,10 +5184,13 @@
         <v>56</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="162" spans="2:5">
+        <v>266</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="162" spans="2:6">
       <c r="B162" s="2">
         <v>2010057</v>
       </c>
@@ -4722,10 +5203,13 @@
         <v>57</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="163" spans="2:5">
+        <v>267</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="163" spans="2:6">
       <c r="B163" s="2">
         <v>2010058</v>
       </c>
@@ -4738,10 +5222,13 @@
         <v>58</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="164" spans="2:5">
+        <v>268</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="2">
         <v>2010059</v>
       </c>
@@ -4754,10 +5241,13 @@
         <v>59</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="165" spans="2:5">
+        <v>269</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="165" spans="2:6">
       <c r="B165" s="2">
         <v>2010060</v>
       </c>
@@ -4770,10 +5260,13 @@
         <v>60</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="166" spans="2:5">
+        <v>270</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="166" spans="2:6">
       <c r="B166" s="2">
         <v>2010061</v>
       </c>
@@ -4786,10 +5279,13 @@
         <v>61</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="167" spans="2:5">
+        <v>271</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="167" spans="2:6">
       <c r="B167" s="2">
         <v>2010062</v>
       </c>
@@ -4802,10 +5298,13 @@
         <v>62</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="168" spans="2:5">
+        <v>272</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="168" spans="2:6">
       <c r="B168" s="2">
         <v>2010063</v>
       </c>
@@ -4818,10 +5317,13 @@
         <v>63</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="169" spans="2:5">
+        <v>273</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
       <c r="B169" s="2">
         <v>2010064</v>
       </c>
@@ -4834,10 +5336,13 @@
         <v>64</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="170" spans="2:5">
+        <v>274</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6">
       <c r="B170" s="2">
         <v>2010065</v>
       </c>
@@ -4850,10 +5355,13 @@
         <v>65</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="171" spans="2:5">
+        <v>275</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="171" spans="2:6">
       <c r="B171" s="2">
         <v>2010066</v>
       </c>
@@ -4866,10 +5374,13 @@
         <v>66</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="172" spans="2:5">
+        <v>276</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="172" spans="2:6">
       <c r="B172" s="2">
         <v>2010067</v>
       </c>
@@ -4882,10 +5393,13 @@
         <v>67</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="173" spans="2:5">
+        <v>277</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6">
       <c r="B173" s="2">
         <v>2010068</v>
       </c>
@@ -4898,10 +5412,13 @@
         <v>68</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="174" spans="2:5">
+        <v>278</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="174" spans="2:6">
       <c r="B174" s="2">
         <v>2010069</v>
       </c>
@@ -4914,10 +5431,13 @@
         <v>69</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="175" spans="2:5">
+        <v>279</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="175" spans="2:6">
       <c r="B175" s="2">
         <v>2010070</v>
       </c>
@@ -4930,10 +5450,13 @@
         <v>70</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="176" spans="2:5">
+        <v>280</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="176" spans="2:6">
       <c r="B176" s="2">
         <v>2010071</v>
       </c>
@@ -4946,10 +5469,13 @@
         <v>71</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="177" spans="2:5">
+        <v>281</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
       <c r="B177" s="2">
         <v>2010072</v>
       </c>
@@ -4962,10 +5488,13 @@
         <v>72</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="178" spans="2:5">
+        <v>282</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="178" spans="2:6">
       <c r="B178" s="2">
         <v>2010073</v>
       </c>
@@ -4978,10 +5507,13 @@
         <v>73</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="179" spans="2:5">
+        <v>283</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
       <c r="B179" s="2">
         <v>2010074</v>
       </c>
@@ -4994,10 +5526,13 @@
         <v>74</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="180" spans="2:5">
+        <v>284</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
       <c r="B180" s="2">
         <v>2010075</v>
       </c>
@@ -5010,10 +5545,13 @@
         <v>75</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="181" spans="2:5">
+        <v>285</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="181" spans="2:6">
       <c r="B181" s="2">
         <v>2010076</v>
       </c>
@@ -5026,10 +5564,13 @@
         <v>76</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="182" spans="2:5">
+        <v>286</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="182" spans="2:6">
       <c r="B182" s="2">
         <v>2010077</v>
       </c>
@@ -5042,10 +5583,13 @@
         <v>77</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="183" spans="2:5">
+        <v>287</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6">
       <c r="B183" s="2">
         <v>2010078</v>
       </c>
@@ -5058,10 +5602,13 @@
         <v>78</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="184" spans="2:5">
+        <v>288</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="184" spans="2:6">
       <c r="B184" s="2">
         <v>2010079</v>
       </c>
@@ -5074,10 +5621,13 @@
         <v>79</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="185" spans="2:5">
+        <v>289</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="185" spans="2:6">
       <c r="B185" s="2">
         <v>2010080</v>
       </c>
@@ -5090,10 +5640,13 @@
         <v>80</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="186" spans="2:5">
+        <v>290</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="186" spans="2:6">
       <c r="B186" s="2">
         <v>2010081</v>
       </c>
@@ -5106,10 +5659,13 @@
         <v>81</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="187" spans="2:5">
+        <v>291</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="187" spans="2:6">
       <c r="B187" s="2">
         <v>2010082</v>
       </c>
@@ -5122,10 +5678,13 @@
         <v>82</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="188" spans="2:5">
+        <v>292</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="188" spans="2:6">
       <c r="B188" s="2">
         <v>2010083</v>
       </c>
@@ -5138,10 +5697,13 @@
         <v>83</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="189" spans="2:5">
+        <v>293</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="189" spans="2:6">
       <c r="B189" s="2">
         <v>2010084</v>
       </c>
@@ -5154,10 +5716,13 @@
         <v>84</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="190" spans="2:5">
+        <v>294</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="190" spans="2:6">
       <c r="B190" s="2">
         <v>2010085</v>
       </c>
@@ -5170,10 +5735,13 @@
         <v>85</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="191" spans="2:5">
+        <v>295</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="191" spans="2:6">
       <c r="B191" s="2">
         <v>2010086</v>
       </c>
@@ -5186,10 +5754,13 @@
         <v>86</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="192" spans="2:5">
+        <v>296</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="192" spans="2:6">
       <c r="B192" s="2">
         <v>2010087</v>
       </c>
@@ -5202,10 +5773,13 @@
         <v>87</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="193" spans="2:5">
+        <v>297</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="193" spans="2:6">
       <c r="B193" s="2">
         <v>2010088</v>
       </c>
@@ -5218,10 +5792,13 @@
         <v>88</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="194" spans="2:5">
+        <v>298</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="194" spans="2:6">
       <c r="B194" s="2">
         <v>2010089</v>
       </c>
@@ -5234,10 +5811,13 @@
         <v>89</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="195" spans="2:5">
+        <v>299</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="195" spans="2:6">
       <c r="B195" s="2">
         <v>2010090</v>
       </c>
@@ -5250,10 +5830,13 @@
         <v>90</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="196" spans="2:5">
+        <v>300</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="196" spans="2:6">
       <c r="B196" s="2">
         <v>2010091</v>
       </c>
@@ -5266,10 +5849,13 @@
         <v>91</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="197" spans="2:5">
+        <v>301</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="197" spans="2:6">
       <c r="B197" s="2">
         <v>2010092</v>
       </c>
@@ -5282,10 +5868,13 @@
         <v>92</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="198" spans="2:5">
+        <v>302</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="198" spans="2:6">
       <c r="B198" s="2">
         <v>2010093</v>
       </c>
@@ -5298,10 +5887,13 @@
         <v>93</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="199" spans="2:5">
+        <v>303</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="2:6">
       <c r="B199" s="2">
         <v>2010094</v>
       </c>
@@ -5314,10 +5906,13 @@
         <v>94</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="200" spans="2:5">
+        <v>304</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="200" spans="2:6">
       <c r="B200" s="2">
         <v>2010095</v>
       </c>
@@ -5330,10 +5925,13 @@
         <v>95</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="201" spans="2:5">
+        <v>305</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="201" spans="2:6">
       <c r="B201" s="2">
         <v>2010096</v>
       </c>
@@ -5346,10 +5944,13 @@
         <v>96</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="202" spans="2:5">
+        <v>306</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="2:6">
       <c r="B202" s="2">
         <v>2010097</v>
       </c>
@@ -5362,10 +5963,13 @@
         <v>97</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="203" spans="2:5">
+        <v>307</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="2:6">
       <c r="B203" s="2">
         <v>2010098</v>
       </c>
@@ -5378,10 +5982,13 @@
         <v>98</v>
       </c>
       <c r="E203" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F203" s="2" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="204" spans="2:5">
+    <row r="204" spans="2:6">
       <c r="B204" s="2">
         <v>2010099</v>
       </c>
@@ -5394,10 +6001,13 @@
         <v>99</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="206" spans="2:5">
+        <v>309</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="206" spans="2:6">
       <c r="B206" s="2">
         <v>3010000</v>
       </c>
@@ -5410,10 +6020,10 @@
         <v>0</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="207" spans="2:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" spans="2:6">
       <c r="B207" s="2">
         <v>3010001</v>
       </c>
@@ -5426,10 +6036,10 @@
         <v>1</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="208" spans="2:5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="208" spans="2:6">
       <c r="B208" s="2">
         <v>3010002</v>
       </c>
@@ -5442,7 +6052,7 @@
         <v>2</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>211</v>
+        <v>15</v>
       </c>
     </row>
     <row r="209" spans="2:5">
@@ -5458,7 +6068,7 @@
         <v>3</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>212</v>
+        <v>17</v>
       </c>
     </row>
     <row r="210" spans="2:5">
@@ -5474,7 +6084,7 @@
         <v>4</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>213</v>
+        <v>19</v>
       </c>
     </row>
     <row r="211" spans="2:5">
@@ -5490,7 +6100,7 @@
         <v>5</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>214</v>
+        <v>21</v>
       </c>
     </row>
     <row r="212" spans="2:5">
@@ -5506,7 +6116,7 @@
         <v>6</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>215</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="2:5">
@@ -5522,7 +6132,7 @@
         <v>7</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>216</v>
+        <v>25</v>
       </c>
     </row>
     <row r="214" spans="2:5">
@@ -5538,7 +6148,7 @@
         <v>8</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>217</v>
+        <v>27</v>
       </c>
     </row>
     <row r="215" spans="2:5">
@@ -5554,7 +6164,7 @@
         <v>9</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>218</v>
+        <v>29</v>
       </c>
     </row>
     <row r="216" spans="2:5">
@@ -5570,7 +6180,7 @@
         <v>10</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>219</v>
+        <v>31</v>
       </c>
     </row>
     <row r="217" spans="2:5">
@@ -5586,7 +6196,7 @@
         <v>11</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>220</v>
+        <v>33</v>
       </c>
     </row>
     <row r="218" spans="2:5">
@@ -5602,7 +6212,7 @@
         <v>12</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>221</v>
+        <v>35</v>
       </c>
     </row>
     <row r="219" spans="2:5">
@@ -5618,7 +6228,7 @@
         <v>13</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>222</v>
+        <v>37</v>
       </c>
     </row>
     <row r="220" spans="2:5">
@@ -5634,7 +6244,7 @@
         <v>14</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>223</v>
+        <v>39</v>
       </c>
     </row>
     <row r="221" spans="2:5">
@@ -5650,7 +6260,7 @@
         <v>15</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>224</v>
+        <v>41</v>
       </c>
     </row>
     <row r="222" spans="2:5">
@@ -5666,7 +6276,7 @@
         <v>16</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>225</v>
+        <v>43</v>
       </c>
     </row>
     <row r="223" spans="2:5">
@@ -5682,7 +6292,7 @@
         <v>17</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>226</v>
+        <v>45</v>
       </c>
     </row>
     <row r="224" spans="2:5">
@@ -5698,7 +6308,7 @@
         <v>18</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>227</v>
+        <v>47</v>
       </c>
     </row>
     <row r="225" spans="2:5">
@@ -5714,7 +6324,7 @@
         <v>19</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>228</v>
+        <v>49</v>
       </c>
     </row>
     <row r="226" spans="2:5">
@@ -5730,7 +6340,7 @@
         <v>20</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>229</v>
+        <v>51</v>
       </c>
     </row>
     <row r="227" spans="2:5">
@@ -5746,7 +6356,7 @@
         <v>21</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>230</v>
+        <v>53</v>
       </c>
     </row>
     <row r="228" spans="2:5">
@@ -5762,7 +6372,7 @@
         <v>22</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>231</v>
+        <v>55</v>
       </c>
     </row>
     <row r="229" spans="2:5">
@@ -5778,7 +6388,7 @@
         <v>23</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>232</v>
+        <v>57</v>
       </c>
     </row>
     <row r="230" spans="2:5">
@@ -5794,7 +6404,7 @@
         <v>24</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>233</v>
+        <v>59</v>
       </c>
     </row>
     <row r="231" spans="2:5">
@@ -5810,7 +6420,7 @@
         <v>25</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>234</v>
+        <v>61</v>
       </c>
     </row>
     <row r="232" spans="2:5">
@@ -5826,7 +6436,7 @@
         <v>26</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>235</v>
+        <v>63</v>
       </c>
     </row>
     <row r="233" spans="2:5">
@@ -5842,7 +6452,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>236</v>
+        <v>65</v>
       </c>
     </row>
     <row r="234" spans="2:5">
@@ -5858,7 +6468,7 @@
         <v>28</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>237</v>
+        <v>67</v>
       </c>
     </row>
     <row r="235" spans="2:5">
@@ -5874,7 +6484,7 @@
         <v>29</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>238</v>
+        <v>69</v>
       </c>
     </row>
     <row r="236" spans="2:5">
@@ -5890,7 +6500,7 @@
         <v>30</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>239</v>
+        <v>71</v>
       </c>
     </row>
     <row r="237" spans="2:5">
@@ -5906,7 +6516,7 @@
         <v>31</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>240</v>
+        <v>73</v>
       </c>
     </row>
     <row r="238" spans="2:5">
@@ -5922,7 +6532,7 @@
         <v>32</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>241</v>
+        <v>75</v>
       </c>
     </row>
     <row r="239" spans="2:5">
@@ -5938,7 +6548,7 @@
         <v>33</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>242</v>
+        <v>77</v>
       </c>
     </row>
     <row r="240" spans="2:5">
@@ -5954,7 +6564,7 @@
         <v>34</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>243</v>
+        <v>79</v>
       </c>
     </row>
     <row r="241" spans="2:5">
@@ -5970,7 +6580,7 @@
         <v>35</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>244</v>
+        <v>81</v>
       </c>
     </row>
     <row r="242" spans="2:5">
@@ -5986,7 +6596,7 @@
         <v>36</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>245</v>
+        <v>83</v>
       </c>
     </row>
     <row r="243" spans="2:5">
@@ -6002,7 +6612,7 @@
         <v>37</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>246</v>
+        <v>85</v>
       </c>
     </row>
     <row r="244" spans="2:5">
@@ -6018,7 +6628,7 @@
         <v>38</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>247</v>
+        <v>87</v>
       </c>
     </row>
     <row r="245" spans="2:5">
@@ -6034,7 +6644,7 @@
         <v>39</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>248</v>
+        <v>89</v>
       </c>
     </row>
     <row r="246" spans="2:5">
@@ -6050,7 +6660,7 @@
         <v>40</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>249</v>
+        <v>91</v>
       </c>
     </row>
     <row r="247" spans="2:5">
@@ -6066,7 +6676,7 @@
         <v>41</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>250</v>
+        <v>93</v>
       </c>
     </row>
     <row r="248" spans="2:5">
@@ -6082,7 +6692,7 @@
         <v>42</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>251</v>
+        <v>95</v>
       </c>
     </row>
     <row r="249" spans="2:5">
@@ -6098,7 +6708,7 @@
         <v>43</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>252</v>
+        <v>97</v>
       </c>
     </row>
     <row r="250" spans="2:5">
@@ -6114,7 +6724,7 @@
         <v>44</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>253</v>
+        <v>99</v>
       </c>
     </row>
     <row r="251" spans="2:5">
@@ -6130,7 +6740,7 @@
         <v>45</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>254</v>
+        <v>101</v>
       </c>
     </row>
     <row r="252" spans="2:5">
@@ -6146,7 +6756,7 @@
         <v>46</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>255</v>
+        <v>103</v>
       </c>
     </row>
     <row r="253" spans="2:5">
@@ -6162,7 +6772,7 @@
         <v>47</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>256</v>
+        <v>105</v>
       </c>
     </row>
     <row r="254" spans="2:5">
@@ -6178,7 +6788,7 @@
         <v>48</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>257</v>
+        <v>107</v>
       </c>
     </row>
     <row r="255" spans="2:5">
@@ -6194,7 +6804,7 @@
         <v>49</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>258</v>
+        <v>109</v>
       </c>
     </row>
     <row r="256" spans="2:5">
@@ -6210,7 +6820,7 @@
         <v>50</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>259</v>
+        <v>111</v>
       </c>
     </row>
     <row r="257" spans="2:5">
@@ -6226,7 +6836,7 @@
         <v>51</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>260</v>
+        <v>113</v>
       </c>
     </row>
     <row r="258" spans="2:5">
@@ -6242,7 +6852,7 @@
         <v>52</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>261</v>
+        <v>115</v>
       </c>
     </row>
     <row r="259" spans="2:5">
@@ -6258,7 +6868,7 @@
         <v>53</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>262</v>
+        <v>117</v>
       </c>
     </row>
     <row r="260" spans="2:5">
@@ -6274,7 +6884,7 @@
         <v>54</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>263</v>
+        <v>119</v>
       </c>
     </row>
     <row r="261" spans="2:5">
@@ -6290,7 +6900,7 @@
         <v>55</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>264</v>
+        <v>121</v>
       </c>
     </row>
     <row r="262" spans="2:5">
@@ -6306,7 +6916,7 @@
         <v>56</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>265</v>
+        <v>123</v>
       </c>
     </row>
     <row r="263" spans="2:5">
@@ -6322,7 +6932,7 @@
         <v>57</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>266</v>
+        <v>125</v>
       </c>
     </row>
     <row r="264" spans="2:5">
@@ -6338,7 +6948,7 @@
         <v>58</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>267</v>
+        <v>127</v>
       </c>
     </row>
     <row r="265" spans="2:5">
@@ -6354,7 +6964,7 @@
         <v>59</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>268</v>
+        <v>129</v>
       </c>
     </row>
     <row r="266" spans="2:5">
@@ -6370,7 +6980,7 @@
         <v>60</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>269</v>
+        <v>131</v>
       </c>
     </row>
     <row r="267" spans="2:5">
@@ -6386,7 +6996,7 @@
         <v>61</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>270</v>
+        <v>133</v>
       </c>
     </row>
     <row r="268" spans="2:5">
@@ -6402,7 +7012,7 @@
         <v>62</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>271</v>
+        <v>135</v>
       </c>
     </row>
     <row r="269" spans="2:5">
@@ -6418,7 +7028,7 @@
         <v>63</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>272</v>
+        <v>137</v>
       </c>
     </row>
     <row r="270" spans="2:5">
@@ -6434,7 +7044,7 @@
         <v>64</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>273</v>
+        <v>139</v>
       </c>
     </row>
     <row r="271" spans="2:5">
@@ -6442,7 +7052,7 @@
         <v>3010065</v>
       </c>
       <c r="C271" s="2">
-        <f t="shared" ref="C271:C302" si="20">IF(B271="","",INT(B271/10000)*10000)</f>
+        <f t="shared" ref="C271:C305" si="20">IF(B271="","",INT(B271/10000)*10000)</f>
         <v>3010000</v>
       </c>
       <c r="D271" s="2">
@@ -6450,7 +7060,7 @@
         <v>65</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>274</v>
+        <v>141</v>
       </c>
     </row>
     <row r="272" spans="2:5">
@@ -6466,7 +7076,7 @@
         <v>66</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>275</v>
+        <v>143</v>
       </c>
     </row>
     <row r="273" spans="2:5">
@@ -6482,7 +7092,7 @@
         <v>67</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>276</v>
+        <v>145</v>
       </c>
     </row>
     <row r="274" spans="2:5">
@@ -6498,7 +7108,7 @@
         <v>68</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>277</v>
+        <v>147</v>
       </c>
     </row>
     <row r="275" spans="2:5">
@@ -6514,7 +7124,7 @@
         <v>69</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>278</v>
+        <v>149</v>
       </c>
     </row>
     <row r="276" spans="2:5">
@@ -6530,7 +7140,7 @@
         <v>70</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>279</v>
+        <v>151</v>
       </c>
     </row>
     <row r="277" spans="2:5">
@@ -6546,7 +7156,7 @@
         <v>71</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>280</v>
+        <v>153</v>
       </c>
     </row>
     <row r="278" spans="2:5">
@@ -6562,7 +7172,7 @@
         <v>72</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>281</v>
+        <v>155</v>
       </c>
     </row>
     <row r="279" spans="2:5">
@@ -6578,7 +7188,7 @@
         <v>73</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>282</v>
+        <v>157</v>
       </c>
     </row>
     <row r="280" spans="2:5">
@@ -6594,7 +7204,7 @@
         <v>74</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>283</v>
+        <v>159</v>
       </c>
     </row>
     <row r="281" spans="2:5">
@@ -6610,7 +7220,7 @@
         <v>75</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
     </row>
     <row r="282" spans="2:5">
@@ -6626,7 +7236,7 @@
         <v>76</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>285</v>
+        <v>163</v>
       </c>
     </row>
     <row r="283" spans="2:5">
@@ -6642,7 +7252,7 @@
         <v>77</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>286</v>
+        <v>165</v>
       </c>
     </row>
     <row r="284" spans="2:5">
@@ -6658,7 +7268,7 @@
         <v>78</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>287</v>
+        <v>167</v>
       </c>
     </row>
     <row r="285" spans="2:5">
@@ -6674,7 +7284,7 @@
         <v>79</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>288</v>
+        <v>169</v>
       </c>
     </row>
     <row r="286" spans="2:5">
@@ -6690,7 +7300,7 @@
         <v>80</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>289</v>
+        <v>171</v>
       </c>
     </row>
     <row r="287" spans="2:5">
@@ -6706,7 +7316,7 @@
         <v>81</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>290</v>
+        <v>173</v>
       </c>
     </row>
     <row r="288" spans="2:5">
@@ -6722,7 +7332,7 @@
         <v>82</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>291</v>
+        <v>175</v>
       </c>
     </row>
     <row r="289" spans="2:5">
@@ -6738,7 +7348,7 @@
         <v>83</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>292</v>
+        <v>177</v>
       </c>
     </row>
     <row r="290" spans="2:5">
@@ -6754,7 +7364,7 @@
         <v>84</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>293</v>
+        <v>179</v>
       </c>
     </row>
     <row r="291" spans="2:5">
@@ -6770,7 +7380,7 @@
         <v>85</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>294</v>
+        <v>181</v>
       </c>
     </row>
     <row r="292" spans="2:5">
@@ -6786,7 +7396,7 @@
         <v>86</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>295</v>
+        <v>183</v>
       </c>
     </row>
     <row r="293" spans="2:5">
@@ -6802,7 +7412,7 @@
         <v>87</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>296</v>
+        <v>185</v>
       </c>
     </row>
     <row r="294" spans="2:5">
@@ -6818,7 +7428,7 @@
         <v>88</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>297</v>
+        <v>187</v>
       </c>
     </row>
     <row r="295" spans="2:5">
@@ -6834,7 +7444,7 @@
         <v>89</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>298</v>
+        <v>189</v>
       </c>
     </row>
     <row r="296" spans="2:5">
@@ -6850,7 +7460,7 @@
         <v>90</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>299</v>
+        <v>191</v>
       </c>
     </row>
     <row r="297" spans="2:5">
@@ -6866,7 +7476,7 @@
         <v>91</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>300</v>
+        <v>193</v>
       </c>
     </row>
     <row r="298" spans="2:5">
@@ -6882,7 +7492,7 @@
         <v>92</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>301</v>
+        <v>195</v>
       </c>
     </row>
     <row r="299" spans="2:5">
@@ -6898,7 +7508,7 @@
         <v>93</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>302</v>
+        <v>197</v>
       </c>
     </row>
     <row r="300" spans="2:5">
@@ -6914,7 +7524,7 @@
         <v>94</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>303</v>
+        <v>199</v>
       </c>
     </row>
     <row r="301" spans="2:5">
@@ -6930,7 +7540,7 @@
         <v>95</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>304</v>
+        <v>201</v>
       </c>
     </row>
     <row r="302" spans="2:5">
@@ -6946,7 +7556,7 @@
         <v>96</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>305</v>
+        <v>203</v>
       </c>
     </row>
     <row r="303" spans="2:5">
@@ -6954,7 +7564,7 @@
         <v>3010097</v>
       </c>
       <c r="C303" s="2">
-        <f>IF(B303="","",INT(B303/10000)*10000)</f>
+        <f t="shared" si="20"/>
         <v>3010000</v>
       </c>
       <c r="D303" s="2">
@@ -6962,7 +7572,7 @@
         <v>97</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>306</v>
+        <v>205</v>
       </c>
     </row>
     <row r="304" spans="2:5">
@@ -6970,7 +7580,7 @@
         <v>3010098</v>
       </c>
       <c r="C304" s="2">
-        <f>IF(B304="","",INT(B304/10000)*10000)</f>
+        <f t="shared" si="20"/>
         <v>3010000</v>
       </c>
       <c r="D304" s="2">
@@ -6978,7 +7588,7 @@
         <v>98</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>307</v>
+        <v>207</v>
       </c>
     </row>
     <row r="305" spans="2:5">
@@ -6986,7 +7596,7 @@
         <v>3010099</v>
       </c>
       <c r="C305" s="2">
-        <f>IF(B305="","",INT(B305/10000)*10000)</f>
+        <f t="shared" si="20"/>
         <v>3010000</v>
       </c>
       <c r="D305" s="2">
@@ -6994,7 +7604,7 @@
         <v>99</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>308</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
